--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,6 +2080,238 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120536915</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598932</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7033610</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120536914</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lidgatu, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>599061</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033712</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2082,7 +2082,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120536915</v>
+        <v>120536914</v>
       </c>
       <c r="B14" t="n">
         <v>90580</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598932</v>
+        <v>599061</v>
       </c>
       <c r="R14" t="n">
-        <v>7033610</v>
+        <v>7033712</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,7 +2198,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120536914</v>
+        <v>120536915</v>
       </c>
       <c r="B15" t="n">
         <v>90580</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599061</v>
+        <v>598932</v>
       </c>
       <c r="R15" t="n">
-        <v>7033712</v>
+        <v>7033610</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,6 +2312,337 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127347809</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>599034</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7033701</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127347779</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>599034</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7033701</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127347096</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>599034</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7033701</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2317,7 +2317,7 @@
         <v>127347809</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>127347779</v>
       </c>
       <c r="B17" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2317,7 +2317,7 @@
         <v>127347809</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>127347779</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2317,7 +2317,7 @@
         <v>127347809</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>127347779</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2317,7 +2317,7 @@
         <v>127347809</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>127347779</v>
       </c>
       <c r="B17" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2541,7 +2541,7 @@
         <v>127347096</v>
       </c>
       <c r="B18" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -2648,7 +2648,7 @@
         <v>134174781</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>134174799</v>
       </c>
       <c r="B20" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101652030</v>
+        <v>110386132</v>
       </c>
       <c r="B2" t="n">
-        <v>5413</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101920</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jättjärn NR, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599005.1872608326</v>
+        <v>598993</v>
       </c>
       <c r="R2" t="n">
-        <v>7033573.06200735</v>
+        <v>7033749</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,31 +743,16 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Eftersökt tidigare kläckhål av raggbock. Lämpliga lågor samt kläckhål som eftersöktes på platsen visade bara större timmerman. Puppkammare grunt under vedytan.</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -794,27 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102849935</v>
+        <v>134175195</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,40 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599088</v>
+        <v>599295</v>
       </c>
       <c r="R3" t="n">
-        <v>7033799</v>
+        <v>7033948</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,34 +855,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Maria Eriksson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Maria Eriksson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109633305</v>
+        <v>134175235</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,45 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599045.3751650122</v>
+        <v>599298</v>
       </c>
       <c r="R4" t="n">
-        <v>7033811.3866691</v>
+        <v>7033950</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110386111</v>
+        <v>110386023</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,13 +1008,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599006.4125571706</v>
+        <v>599201</v>
       </c>
       <c r="R5" t="n">
-        <v>7033808.835337584</v>
+        <v>7033981</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,19 +1041,9 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,37 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110386012</v>
+        <v>110386047</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599218.1451924867</v>
+        <v>599172</v>
       </c>
       <c r="R6" t="n">
-        <v>7033970.456017767</v>
+        <v>7033982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,19 +1142,9 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,15 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110386047</v>
+        <v>110386062</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599172.0155996771</v>
+        <v>599164</v>
       </c>
       <c r="R7" t="n">
-        <v>7033982.020318707</v>
+        <v>7033975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,19 +1243,9 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,57 +1273,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110386096</v>
+        <v>120536914</v>
       </c>
       <c r="B8" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599188.1164736182</v>
+        <v>599061</v>
       </c>
       <c r="R8" t="n">
-        <v>7033839.115941501</v>
+        <v>7033712</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,22 +1342,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,34 +1366,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110386177</v>
+        <v>120536915</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,45 +1395,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598918.4994171957</v>
+        <v>598932</v>
       </c>
       <c r="R9" t="n">
-        <v>7033647.913371036</v>
+        <v>7033610</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,22 +1453,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,69 +1483,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110386039</v>
+        <v>127347096</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599181.0409789827</v>
+        <v>599034</v>
       </c>
       <c r="R10" t="n">
-        <v>7033994.847864725</v>
+        <v>7033701</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,22 +1560,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,34 +1584,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110386132</v>
+        <v>134175031</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,40 +1613,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598993.0133763143</v>
+        <v>599297</v>
       </c>
       <c r="R11" t="n">
-        <v>7033748.815949801</v>
+        <v>7033965</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,22 +1667,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,7 +1681,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1850,15 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110386120</v>
+        <v>134175186</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,40 +1710,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Ång</t>
+          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598993.0133763143</v>
+        <v>599295</v>
       </c>
       <c r="R12" t="n">
-        <v>7033748.815949801</v>
+        <v>7033948</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1923,22 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,7 +1778,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1966,37 +1796,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110386062</v>
+        <v>110386120</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599164.168398972</v>
+        <v>598993</v>
       </c>
       <c r="R13" t="n">
-        <v>7033974.606841364</v>
+        <v>7033749</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,19 +1867,9 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,57 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120536915</v>
+        <v>134174966</v>
       </c>
       <c r="B14" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598932</v>
+        <v>599304</v>
       </c>
       <c r="R14" t="n">
-        <v>7033610</v>
+        <v>7033964</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,22 +1962,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,27 +1982,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120536914</v>
+        <v>110386012</v>
       </c>
       <c r="B15" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,41 +2005,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lidgatu, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599061</v>
+        <v>599218</v>
       </c>
       <c r="R15" t="n">
-        <v>7033712</v>
+        <v>7033971</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,22 +2062,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,28 +2076,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127347809</v>
+        <v>120536916</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,42 +2106,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599034</v>
+        <v>599220</v>
       </c>
       <c r="R16" t="n">
-        <v>7033701</v>
+        <v>7033975</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2384,27 +2164,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,60 +2194,63 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127347779</v>
+        <v>102849935</v>
       </c>
       <c r="B17" t="n">
-        <v>58042</v>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599034</v>
+        <v>599088</v>
       </c>
       <c r="R17" t="n">
-        <v>7033701</v>
+        <v>7033799</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2496,22 +2274,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:42</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:42</t>
+          <t>2022-08-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,66 +2288,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anna-Maria Eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anna-Maria Eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127347096</v>
+        <v>134174781</v>
       </c>
       <c r="B18" t="n">
-        <v>91352</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599034</v>
+        <v>599267</v>
       </c>
       <c r="R18" t="n">
-        <v>7033701</v>
+        <v>7033953</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,22 +2372,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,22 +2392,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134174781</v>
+        <v>134174799</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,21 +2415,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2680,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599267</v>
+        <v>599294</v>
       </c>
       <c r="R19" t="n">
-        <v>7033953</v>
+        <v>7033975</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2742,10 +2501,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134174799</v>
+        <v>110386111</v>
       </c>
       <c r="B20" t="n">
-        <v>83351</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,37 +2512,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blåbärshällorna, Blåbärshällorna, Ång</t>
+          <t>Blåbärshällorna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599294</v>
+        <v>599006</v>
       </c>
       <c r="R20" t="n">
-        <v>7033975</v>
+        <v>7033809</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2807,12 +2569,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,6 +2583,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2836,6 +2599,859 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>109633294</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>599201</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7033981</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>109633305</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>599045</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7033811</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110386177</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>598918</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7033648</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127347809</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>599034</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7033701</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>109633301</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>599201</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7033981</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>9 ägg i redet</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127347779</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>599034</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7033701</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>110386096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>599188</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7033839</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>110386039</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blåbärshällorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>599181</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7033995</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11491-2022 artfynd.xlsx
+++ b/artfynd/A 11491-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386132</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134175195</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134175235</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386047</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386062</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536915</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347096</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134175031</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134175186</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386120</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134174966</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2092,6 +2162,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386012</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120536916</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102849935</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134174781</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,6 +2588,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134174799</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386111</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2704,6 +2804,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633294</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633305</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386177</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3031,6 +3146,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347809</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3141,6 +3261,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633301</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3248,6 +3373,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127347779</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3350,6 +3480,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386096</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3452,8 +3587,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110386039</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>